--- a/xls/square_high_un_16_tri3_10.xlsx
+++ b/xls/square_high_un_16_tri3_10.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>165</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>340</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>97</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>480</v>
+      </c>
+      <c r="I8">
+        <v>23.00633292255631</v>
+      </c>
+      <c r="J8">
+        <v>7.455993521884071</v>
+      </c>
+      <c r="K8">
+        <v>7.903397985229829</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>165</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>340</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>122</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <v>618</v>
+      </c>
+      <c r="I9">
+        <v>-0.3968502393714108</v>
+      </c>
+      <c r="J9">
+        <v>-1.1387016486849573</v>
+      </c>
+      <c r="K9">
+        <v>-0.4244618863514099</v>
+      </c>
+    </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>11</v>
